--- a/Plotting/production_shares_ammonia_scope.xlsx
+++ b/Plotting/production_shares_ammonia_scope.xlsx
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1182600.000000001</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>141966.0804876869</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -532,7 +532,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1040633.919512313</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -545,10 +545,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1021797.902093929</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1011554.504091532</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>160802.0979060706</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>25.06875995371944</v>
       </c>
       <c r="D8" t="n">
-        <v>950210.4117988135</v>
+        <v>1011669.670771167</v>
       </c>
     </row>
     <row r="9">
